--- a/result.xlsx
+++ b/result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeanxu/Documents/UniLU/9ComputationalStatistic/Project-21/ComputationalStatistic-project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{831759BC-39C9-2642-B5B4-4FB2A2394B74}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D736E241-034F-E34D-BAEB-85F6AAB6B0E1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="460" windowWidth="28440" windowHeight="19540" xr2:uid="{433B9734-98A9-8D4A-BFED-91FFC69DD3E9}"/>
   </bookViews>
@@ -33,18 +33,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="29">
-  <si>
-    <t>Empirical Tests</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
   <si>
     <t xml:space="preserve">Gap Test </t>
   </si>
   <si>
     <t xml:space="preserve"> Serial Test</t>
-  </si>
-  <si>
-    <t>Equidistribution Test</t>
   </si>
   <si>
     <t>X1</t>
@@ -123,6 +117,9 @@
   <si>
     <t xml:space="preserve"> Kolmogorov–
 Smirnov Test</t>
+  </si>
+  <si>
+    <t>Frequency Test</t>
   </si>
 </sst>
 </file>
@@ -182,7 +179,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -206,43 +203,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color indexed="64"/>
@@ -334,7 +294,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -361,41 +321,50 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -730,100 +699,98 @@
     <col min="15" max="16" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B2" s="17"/>
-      <c r="C2" s="13" t="s">
+    <row r="2" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="14"/>
+      <c r="C2" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="16"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="11"/>
+      <c r="H2" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" s="14"/>
-      <c r="H2" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="12"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="20"/>
     </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B3" s="18"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" s="11"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="L3" s="11"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="O3" s="11"/>
-      <c r="P3" s="12"/>
+    <row r="3" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="15"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="21"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="22"/>
     </row>
     <row r="4" spans="2:16" ht="50" x14ac:dyDescent="0.3">
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="G4" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="21" t="s">
+      <c r="I4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J4" s="21" t="s">
+      <c r="L4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M4" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M4" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>11</v>
-      </c>
       <c r="O4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P4" s="21" t="s">
-        <v>9</v>
+        <v>6</v>
+      </c>
+      <c r="P4" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5" s="5">
         <v>15396</v>
@@ -832,7 +799,7 @@
         <v>19</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="9"/>
@@ -843,7 +810,7 @@
         <v>13</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K5" s="3">
         <v>44</v>
@@ -852,21 +819,21 @@
         <v>63</v>
       </c>
       <c r="M5" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="N5" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="O5" s="3">
         <v>15</v>
       </c>
       <c r="P5" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C6" s="7">
         <v>11632</v>
@@ -875,18 +842,18 @@
         <v>19</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="9"/>
       <c r="H6" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I6" s="3">
         <v>13</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K6" s="3">
         <v>64</v>
@@ -895,21 +862,21 @@
         <v>63</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="O6" s="6">
         <v>15</v>
       </c>
       <c r="P6" s="9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C7" s="7">
         <v>12627</v>
@@ -918,13 +885,13 @@
         <v>19</v>
       </c>
       <c r="E7" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="8" t="s">
         <v>14</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>16</v>
       </c>
       <c r="H7" s="3">
         <v>13</v>
@@ -933,7 +900,7 @@
         <v>12</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K7" s="3">
         <v>39</v>
@@ -955,13 +922,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
     <mergeCell ref="C2:E3"/>
     <mergeCell ref="B2:B3"/>
-    <mergeCell ref="H2:P2"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="H2:J3"/>
+    <mergeCell ref="K2:M3"/>
+    <mergeCell ref="N2:P3"/>
     <mergeCell ref="F2:G3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
